--- a/output/2026-09-07_03_Slovenia_Goriska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-07_03_Slovenia_Goriska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Filiale di Bartog d.o.o. Trebnje (Kromberk, Industrijska cesta 2). Vendita al dettaglio/ingrosso di pneumatici, ricambi auto, utensili e attrezzatura da officina. Esistenza e recapiti confermati via WebSearch (bizi.si, itis.siol.net, robin.si, sito aziendale)</t>
+          <t>Filiale di Bartog d.o.o. Trebnje (Kromberk, Industrijska cesta 2). Vendita al dettaglio/ingrosso di pneumatici, ricambi auto, utensili e attrezzatura da officina. Esistenza e recapiti confermati via WebSearch (bizi.si, itis.siol.net, robin.si, sito aziendale) [DUPLICATO — vedi anche: 2026-09-06_18_Slovenia_Primorsko-notranjska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -547,10 +547,9 @@
           <t>(05) 330 32 00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Punto vendita Merkur (Vipavska cesta 53, Rozna Dolina). Rivenditore di utensili manuali/elettrici, ferramenta e materiale da costruzione, con linea di vendita B2B (Prodaja podjetjem). Esistenza e recapiti confermati via WebSearch (itis.siol.net, saint-gobain.si, opendi.si)</t>
+          <t>Punto vendita Merkur (Vipavska cesta 53, Rozna Dolina). Rivenditore di utensili manuali/elettrici, ferramenta e materiale da costruzione, con linea di vendita B2B (Prodaja podjetjem). Esistenza e recapiti confermati via WebSearch (itis.siol.net, saint-gobain.si, opendi.si) [DUPLICATO — vedi anche: 2026-09-05_20_Slovenia_Pomurska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -590,7 +589,6 @@
           <t>05 334 33 26</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Centro tecnico Mercator (Industrijska cesta 6), incluso nella rete Cash &amp; Carry (veleprodaja) del gruppo Mercator</t>
@@ -685,7 +683,6 @@
           <t>(05) 330 57 62</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Rivenditore autorizzato Bosch Professional (Industrijska cesta 5)</t>
@@ -733,10 +730,9 @@
           <t>041 620 775</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Punto vendita/terenska prodaja di Inter diskont presso ex negozio Lipa ad Ajdovscina. Rivenditore di utensili elettrici, pneumatici, saldatura e accessori/attrezzatura da officina. Esistenza e recapiti confermati via WebSearch (interdiskont.si)</t>
+          <t>Punto vendita/terenska prodaja di Inter diskont presso ex negozio Lipa ad Ajdovscina. Rivenditore di utensili elettrici, pneumatici, saldatura e accessori/attrezzatura da officina. Esistenza e recapiti confermati via WebSearch (interdiskont.si) [DUPLICATO — vedi anche: 2026-09-05_21_Slovenia_Pomurska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
